--- a/光伏配储项目/电价数据/2026/联禾站.xlsx
+++ b/光伏配储项目/电价数据/2026/联禾站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48892</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7559900000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54796</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.56004</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.48297</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47523</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.18136</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23921</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.05242</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01148</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.08709</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.05791</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.16801</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.17197</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.15737</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53363</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.1165</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.15757</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6610199999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.85894</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19042</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.49042</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.34164</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.99782</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.27569</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.56083</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67686</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.72722</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.1063</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89019</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76095</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51524</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48313</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46558</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42736</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7164400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8874299999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.93952</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50178</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5240199999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50886</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50902</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49102</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47256</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44296</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.12744</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.98476</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.04984</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.48851</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48342</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50471</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.16681</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.10475</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.61514</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.004030000000000001</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.03357</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.70621</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.63632</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.00117</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.2069</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.82482</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.19136</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.61021</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59811</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7468899999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16062</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24646</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13857</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8395499999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20458</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10558</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25639</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02389</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08992</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65019</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98282</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91274</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95897</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78767</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.89671</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.74303</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77548</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7343200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76558</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3349</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5126900000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44548</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43127</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47727</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.9564199999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.90008</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22904</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.95489</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.01502</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.44454</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78416</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.49935</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28365</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6206799999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64095</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50606</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.47647</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61498</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48405</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61694</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55813</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7231599999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5235299999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5603400000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3423</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5164099999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43056</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.12511</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.17945</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.08555</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56914</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.17655</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6215599999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50795</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46653</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47496</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.4903</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.55232</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55725</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49127</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46722</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32112</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.13976</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09368000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.11323</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13518</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.13546</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.19735</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.19653</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.07049</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.02055</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.03338</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01572</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.53991</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.36863</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.82873</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.55363</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.52686</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.40665</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5730499999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10221</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.007019999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04642</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.16105</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34571</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32257</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854500000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8690399999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5649</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33082</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53076</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53927</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39986</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62182</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45227</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.44098</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.65618</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.49333</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62336</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.80383</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88344</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47082</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.48544</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6545800000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.49193</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.0226</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.7773300000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8724299999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87502</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.5046700000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.81651</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5915900000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4704100000000001</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.52764</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.36915</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93359</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.46892</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.53952</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5971900000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.43535</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.23248</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.10229</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20052</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.52077</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.75612</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.93925</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48049</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1963</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72565</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8174199999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.67679</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.77093</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.57562</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47252</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46132</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.48902</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43652</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47059</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5978600000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45427</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.53527</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44187</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.50919</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.49871</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.41759</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.46416</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.44278</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6190800000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5229400000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15751</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26398</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25846</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.44328</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.64076</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.99581</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.54196</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5097699999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.50401</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.36319</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.50471</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5192100000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5104300000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.47815</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.08269</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10534</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.12065</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09873999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26374</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23288</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13894</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.06377000000000001</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.06745999999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16712</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.53062</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.53088</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.51728</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.51374</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.52008</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.38455</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6595800000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.55301</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.47379</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42087</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5300199999999999</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24256</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23051</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21913</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.21602</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.81835</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.42517</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.38964</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6143500000000001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.6224299999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.14472</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6784600000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46172</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.19581</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.22825</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5817100000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.02847</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58575</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71562</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.01074</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.86653</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.7031499999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5257500000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.62419</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.4128</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.50401</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45934</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.49101</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.44363</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36572</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.5615399999999999</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.03437</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.51309</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5335800000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.36958</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26064</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11209</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.20875</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.18257</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.13676</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.19447</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.22797</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25627</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.16347</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.22275</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.25296</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.54432</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6327200000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.64828</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.62539</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84282</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.14193</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.63589</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.58694</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.47626</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38565</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.57684</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.70629</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.61552</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.87526</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.46967</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.44812</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.46151</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.47852</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43109</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.47571</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.45313</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.46865</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45743</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.54331</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.53286</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5274099999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5964299999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.52376</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46598</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47057</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.55118</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64774</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.87803</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.46207</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43056</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.46355</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.58324</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.52463</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.61941</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6215499999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.68392</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.91453</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.12851</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.24172</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.89432</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.06079</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.88617</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.67426</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.10133</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78584</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6393099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6885599999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.54696</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.57531</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5622999999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5541799999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.46941</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.6751200000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.48645</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.50802</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.53128</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43228</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.46694</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.58402</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.94374</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.15659</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5099</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.11799</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.45561</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5124500000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45923</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.48774</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.50388</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.42609</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.46628</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.50875</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.45172</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.60697</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.48016</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.48342</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.44784</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.46702</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.5884299999999999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.55932</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.56609</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.53023</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.51586</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.51416</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.5274500000000001</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.18814</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.21493</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.10107</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.12042</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.19006</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21705</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.48311</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.45694</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43162</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.48471</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.44522</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.41355</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.47689</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.48648</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.47908</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.47908</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.47672</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.47933</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.47378</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.48676</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.48635</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.49014</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03115</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00073</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15087</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02252</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01493</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04305</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04098</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02943</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03984</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03654</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01543</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03566</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.52486</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.39967</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.12961</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.96774</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8202699999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5093</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.52486</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5727899999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.46353</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.59377</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.6148899999999999</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.5295700000000001</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.6043099999999999</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.55521</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.57609</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.5639400000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.5871499999999999</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.51622</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.55314</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.50214</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.40206</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.33667</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86888</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.05118</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.03263</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.01264</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.03208</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.02052</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.47558</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.43124</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.01607</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03852000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.01117</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.03407</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.01325</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.10457</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.06988</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.09258</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.0206</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.10338</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86009</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.85833</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.95935</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.0938</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.09935</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.08918</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.41488</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.58751</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.85764</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.36619</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.8052999999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5156799999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.6034700000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.50384</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.50912</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6439199999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.45285</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.5127200000000001</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.48822</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.64759</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.50639</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.26569</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.13986</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.16943</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.03890999999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.15705</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26105</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42487</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.18325</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.87624</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.59477</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4402799999999999</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5328200000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.52374</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6524500000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.39587</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.48896</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.4685299999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44701</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5321699999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8227599999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.98354</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.80345</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.74578</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.92541</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82886</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.56552</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55465</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.63862</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81777</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.55821</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.90046</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.7792100000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5939500000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43614</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.44089</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27716</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.39718</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.52138</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41082</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42858</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44223</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66615</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.60092</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7604299999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53746</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7583799999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.47087</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.92459</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.9878899999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.46908</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48807</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40136</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.44772</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.57014</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.43611</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17952</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.21215</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09570000000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05977</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02676</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05522999999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11368</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01541</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20929</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.53722</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45174</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.51098</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47027</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44115</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.47196</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41288</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.22274</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.03845000000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.20549</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41178</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23164</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27422</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00267</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3857</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47451</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17661</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14625</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19938</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00548</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.02603</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.00925</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03229</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13801</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.03304</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.09164</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18187</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22984</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16117</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.00414</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.23696</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.06693</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20191</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14725</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25799</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41406</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40575</v>
       </c>
     </row>
   </sheetData>
